--- a/resources/codebaseline.xlsx
+++ b/resources/codebaseline.xlsx
@@ -13,10 +13,10 @@
     <sheet name="M673_metadata" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="M678" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="M678_metadata" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Z517" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Z517_metadata" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Z571" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Z571_metadata" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Z571" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Z571_metadata" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Z517" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Z517_metadata" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Z571</t>
+          <t>Z517</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T10:32:34.653160</t>
+          <t>2026-08-14T10:10:27.374786</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -5812,11 +5812,7 @@
           <t>defect_multipliers_signature</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>G向ELA Mura=0;G向单亮线=0.5;G向单暗线=0.8;G向带状Mura=0;Short Test NG=0.2;S向ELA Mura=0;S向亮线=0.7;TP复测NG=2;彩斑Mura=0.7</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15063,7 +15059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15096,12 +15092,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -15110,700 +15106,2563 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.00073</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G向单亮线</t>
+          <t>G3亮点</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.00391</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>34056</v>
+        <v>38206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G向单暗线</t>
+          <t>G向单亮线</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.00335</v>
+        <v>0.00058</v>
       </c>
       <c r="E4" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>G向群亮线</t>
+          <t>G向单暗线</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3e-05</v>
+        <v>0.00296</v>
       </c>
       <c r="E5" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>G向群暗线</t>
+          <t>G向彩色带状Mura</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.00015</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>34056</v>
+        <v>38196</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RGB亮点</t>
+          <t>G向微亮线</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Short Test NG</t>
+          <t>G向线状Mura</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.00117</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>34056</v>
+        <v>38206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S向亮线</t>
+          <t>G向群亮线</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02141</v>
+        <v>0.00016</v>
       </c>
       <c r="E9" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S向单暗线</t>
+          <t>G向群暗线</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.00244</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S向带状Mura</t>
+          <t>G彩短条Mura</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3e-05</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S向群亮线</t>
+          <t>HBM亮点</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>34056</v>
+        <v>38204</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S向群暗线</t>
+          <t>L3亮点</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S向边缘Mura</t>
+          <t>PCD裂纹亮线</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6e-05</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>34056</v>
+        <v>38204</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>单亮点</t>
+          <t>RGB亮点</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.00109</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>右斜黑色带状Mura</t>
+          <t>RGB斑</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3e-05</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>34056</v>
+        <v>38196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大圆环Mura</t>
+          <t>RGB黑斑</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3e-05</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>34056</v>
+        <v>38204</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>大面积亮点</t>
+          <t>Short Test NG</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.00012</v>
+        <v>0.001</v>
       </c>
       <c r="E18" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>大面积片状彩斑Mura</t>
+          <t>S向亮线</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3e-05</v>
+        <v>0.00605</v>
       </c>
       <c r="E19" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>孔区S向分屏</t>
+          <t>S向单暗线</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3e-05</v>
+        <v>0.00432</v>
       </c>
       <c r="E20" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>常亮白斑</t>
+          <t>S向带状Mura</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.00038</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>常暗黑斑Mura</t>
+          <t>S向微亮线</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.00159</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>34056</v>
+        <v>38196</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>彩斑Mura</t>
+          <t>S向棱形彩色带状Mura</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.00079</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>微亮点</t>
+          <t>S向群亮线</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.00012</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>斑中带点</t>
+          <t>S向群暗线</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3e-05</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>暗点</t>
+          <t>S向边缘Mura</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.00476</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>流星状划线</t>
+          <t>TP复测OK</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3e-05</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>34056</v>
+        <v>38196</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>灰阶点状白斑Mura</t>
+          <t>切屏黑斑</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3e-05</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>34056</v>
+        <v>38196</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>白画面黑斑Mura</t>
+          <t>单亮点</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>34056</v>
+        <v>38198</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>群亮点</t>
+          <t>可修复亮点</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.00117</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>34056</v>
+        <v>38196</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>群暗点</t>
+          <t>右斜黑色带状Mura</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.00373</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>34056</v>
+        <v>38204</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>大圆环Mura</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>大面积亮点</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>大面积暗点</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>大面积片状彩斑Mura</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>38204</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>孔区跑道Mura</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>左斜黑色带状Mura</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>38196</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>常亮白斑</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>常暗黑斑Mura</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>彩斑Mura</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>38204</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>微亮点</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>38204</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>微暗点</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>38204</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>斑中带点</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>38206</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>暗点</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>流星状划线</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>灰阶块状白斑Mura</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>38196</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>灰阶小白斑Mura</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>灰阶暗点</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>38204</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>灰阶点状白斑Mura</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>环状Mura</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>38204</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>白画面黑斑Mura</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>群亮点</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>群暗点</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>通道接地短路</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>38203</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>通道间短路</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>38203</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>雪花状Mura</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>38196</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>青/粉斑Mura</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>38198</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B暗点</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="E58" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>G3亮点</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="E59" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>G向单亮线</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.00054</v>
+      </c>
+      <c r="E60" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>G向单暗线</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.00298</v>
+      </c>
+      <c r="E61" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>G向彩色带状Mura</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="E62" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>G向微亮线</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>3e-05</v>
       </c>
-      <c r="E32" t="n">
-        <v>34056</v>
+      <c r="E63" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>G向线状Mura</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>G向群亮线</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="E65" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>G向群暗线</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="E66" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>G彩短条Mura</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E67" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HBM亮点</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="E68" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>L3亮点</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>4e-05</v>
+      </c>
+      <c r="E69" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PCD裂纹亮线</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>RGB亮点</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="E71" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>RGB斑</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>332708</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>RGB黑斑</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="E73" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Short Test NG</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="E74" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>S向亮线</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="E75" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>S向单暗线</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.00318</v>
+      </c>
+      <c r="E76" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>S向带状Mura</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.00031</v>
+      </c>
+      <c r="E77" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>S向微亮线</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>S向棱形彩色带状Mura</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>S向群亮线</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>4e-05</v>
+      </c>
+      <c r="E80" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>S向群暗线</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="E81" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>S向边缘Mura</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E82" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TP复测OK</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>332708</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>切屏黑斑</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="E84" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>单亮点</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.00052</v>
+      </c>
+      <c r="E85" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>可修复亮点</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>右斜黑色带状Mura</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>大圆环Mura</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="E88" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>大面积亮点</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E89" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>大面积暗点</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>大面积片状彩斑Mura</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="E91" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>孔区跑道Mura</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="E92" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>左斜黑色带状Mura</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="E93" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>常亮白斑</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.00182</v>
+      </c>
+      <c r="E94" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>常暗黑斑Mura</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="E95" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>彩斑Mura</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="E96" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>微亮点</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="E97" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>微暗点</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="E98" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>斑中带点</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>暗点</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="E100" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>流星状划线</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>6.999999999999999e-05</v>
+      </c>
+      <c r="E101" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>灰阶块状白斑Mura</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>332708</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>灰阶小白斑Mura</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="E103" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>灰阶暗点</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="E104" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>灰阶点状白斑Mura</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>6.999999999999999e-05</v>
+      </c>
+      <c r="E105" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>环状Mura</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>白画面黑斑Mura</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.00067</v>
+      </c>
+      <c r="E107" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>群亮点</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.00142</v>
+      </c>
+      <c r="E108" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>群暗点</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.00403</v>
+      </c>
+      <c r="E109" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>通道接地短路</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>332712</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>通道间短路</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>332712</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>雪花状Mura</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>332687</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>青/粉斑Mura</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>332687</v>
       </c>
     </row>
   </sheetData>
@@ -15840,7 +17699,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Z517</t>
+          <t>Z571</t>
         </is>
       </c>
     </row>
@@ -15852,7 +17711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T11:23:54.411462</t>
+          <t>2026-08-14T10:07:46.404044</t>
         </is>
       </c>
     </row>
@@ -15888,7 +17747,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -15900,7 +17759,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -15912,7 +17771,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>112</t>
         </is>
       </c>
     </row>
@@ -15922,7 +17781,11 @@
           <t>defect_multipliers_signature</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G向ELA Mura=0;G向单亮线=0.5;G向单暗线=0.8;G向带状Mura=0;Short Test NG=0.2;S向ELA Mura=0;S向亮线=0.7;TP复测NG=2;彩斑Mura=0.7</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15935,7 +17798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15968,12 +17831,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -15982,44 +17845,44 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.00073</v>
       </c>
       <c r="E2" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G3亮点</t>
+          <t>G向ELA Mura</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>38206</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -16028,21 +17891,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.00058</v>
+        <v>0.00391</v>
       </c>
       <c r="E4" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -16051,2356 +17914,723 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.00296</v>
+        <v>0.00335</v>
       </c>
       <c r="E5" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>G向彩色带状Mura</t>
+          <t>G向带状Mura</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>38196</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>G向微亮线</t>
+          <t>G向群亮线</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>G向线状Mura</t>
+          <t>G向群暗线</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.00015</v>
       </c>
       <c r="E8" t="n">
-        <v>38206</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>G向群亮线</t>
+          <t>G彩短条Mura</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.00016</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>G向群暗线</t>
+          <t>RGB亮点</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>G彩短条Mura</t>
+          <t>RGB黑斑</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HBM亮点</t>
+          <t>Short Test NG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.00117</v>
       </c>
       <c r="E12" t="n">
-        <v>38204</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L3亮点</t>
+          <t>S向亮线</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.02141</v>
       </c>
       <c r="E13" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PCD裂纹亮线</t>
+          <t>S向单暗线</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.00244</v>
       </c>
       <c r="E14" t="n">
-        <v>38204</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RGB亮点</t>
+          <t>S向带状Mura</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RGB黑斑</t>
+          <t>S向群亮线</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>38204</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Short Test NG</t>
+          <t>S向群暗线</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S向亮线</t>
+          <t>S向边缘Mura</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.00605</v>
+        <v>6e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S向单暗线</t>
+          <t>单亮点</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.00432</v>
+        <v>0.00109</v>
       </c>
       <c r="E19" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S向带状Mura</t>
+          <t>右斜黑色带状Mura</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E20" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S向微亮线</t>
+          <t>大圆环Mura</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E21" t="n">
-        <v>38196</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S向棱形彩色带状Mura</t>
+          <t>大面积亮点</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
       <c r="E22" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S向群亮线</t>
+          <t>大面积片状彩斑Mura</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E23" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S向群暗线</t>
+          <t>孔区S向分屏</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E24" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S向边缘Mura</t>
+          <t>常亮白斑</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.00038</v>
       </c>
       <c r="E25" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>切屏黑斑</t>
+          <t>常暗黑斑Mura</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.00159</v>
       </c>
       <c r="E26" t="n">
-        <v>38196</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>单亮点</t>
+          <t>彩斑Mura</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.00079</v>
       </c>
       <c r="E27" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>可修复亮点</t>
+          <t>微亮点</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
       <c r="E28" t="n">
-        <v>38196</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>右斜黑色带状Mura</t>
+          <t>斑中带点</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E29" t="n">
-        <v>38204</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>大圆环Mura</t>
+          <t>暗点</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.00476</v>
       </c>
       <c r="E30" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>大面积亮点</t>
+          <t>流星状划线</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E31" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>大面积暗点</t>
+          <t>灰阶点状白斑Mura</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>大面积片状彩斑Mura</t>
+          <t>白画面黑斑Mura</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E33" t="n">
-        <v>38204</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>孔区跑道Mura</t>
+          <t>群亮点</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.00117</v>
       </c>
       <c r="E34" t="n">
-        <v>38198</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>左斜黑色带状Mura</t>
+          <t>群暗点</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.00373</v>
       </c>
       <c r="E35" t="n">
-        <v>38196</v>
+        <v>34056</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>常亮白斑</t>
+          <t>雪花状Mura</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="E36" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>常暗黑斑Mura</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>彩斑Mura</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>38204</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>微亮点</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>38204</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>微暗点</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>38204</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>斑中带点</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>38206</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>暗点</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>流星状划线</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>灰阶小白斑Mura</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>灰阶暗点</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>38204</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>灰阶点状白斑Mura</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>环状Mura</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>38204</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>白画面黑斑Mura</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>群亮点</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>群暗点</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>通道接地短路</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>38203</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>通道间短路</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>38203</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>雪花状Mura</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>38196</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>青/粉斑Mura</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>38198</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>B暗点</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0.00136</v>
-      </c>
-      <c r="E55" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>G3亮点</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="E56" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>G向单亮线</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0.00054</v>
-      </c>
-      <c r="E57" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>G向单暗线</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>0.00298</v>
-      </c>
-      <c r="E58" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>G向彩色带状Mura</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="E59" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>G向微亮线</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="E60" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>G向线状Mura</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>G向群亮线</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>8.000000000000001e-05</v>
-      </c>
-      <c r="E62" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>G向群暗线</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>0.00022</v>
-      </c>
-      <c r="E63" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>G彩短条Mura</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="E64" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>HBM亮点</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2e-05</v>
-      </c>
-      <c r="E65" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>L3亮点</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>4e-05</v>
-      </c>
-      <c r="E66" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>PCD裂纹亮线</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>RGB亮点</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2e-05</v>
-      </c>
-      <c r="E68" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>RGB黑斑</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="E69" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Short Test NG</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>6e-05</v>
-      </c>
-      <c r="E70" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>S向亮线</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>0.00405</v>
-      </c>
-      <c r="E71" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>S向单暗线</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0.00318</v>
-      </c>
-      <c r="E72" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>S向带状Mura</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0.00031</v>
-      </c>
-      <c r="E73" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>S向微亮线</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>S向棱形彩色带状Mura</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>S向群亮线</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>4e-05</v>
-      </c>
-      <c r="E76" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>S向群暗线</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="E77" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>S向边缘Mura</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="E78" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>切屏黑斑</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="E79" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>单亮点</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>0.00052</v>
-      </c>
-      <c r="E80" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>可修复亮点</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>右斜黑色带状Mura</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>大圆环Mura</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="E83" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>大面积亮点</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="E84" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>大面积暗点</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>大面积片状彩斑Mura</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="E86" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>孔区跑道Mura</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="E87" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>左斜黑色带状Mura</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="E88" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>常亮白斑</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>0.00182</v>
-      </c>
-      <c r="E89" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>常暗黑斑Mura</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>0.00106</v>
-      </c>
-      <c r="E90" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>彩斑Mura</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0.00243</v>
-      </c>
-      <c r="E91" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>微亮点</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>2e-05</v>
-      </c>
-      <c r="E92" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>微暗点</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="E93" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>斑中带点</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>暗点</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>0.00419</v>
-      </c>
-      <c r="E95" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>流星状划线</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>6.999999999999999e-05</v>
-      </c>
-      <c r="E96" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>灰阶小白斑Mura</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="E97" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>灰阶暗点</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="E98" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>灰阶点状白斑Mura</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>6.999999999999999e-05</v>
-      </c>
-      <c r="E99" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>环状Mura</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>白画面黑斑Mura</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>0.00067</v>
-      </c>
-      <c r="E101" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>群亮点</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>0.00142</v>
-      </c>
-      <c r="E102" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>群暗点</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>0.00403</v>
-      </c>
-      <c r="E103" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>通道接地短路</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
-        <v>332712</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>通道间短路</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="n">
-        <v>332712</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>雪花状Mura</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="n">
-        <v>332687</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>青/粉斑Mura</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="n">
-        <v>332687</v>
+        <v>34056</v>
       </c>
     </row>
   </sheetData>
